--- a/Result/profitability/8261.xlsx
+++ b/Result/profitability/8261.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.25125</v>
+        <v>1.27625</v>
       </c>
       <c r="N2" t="n">
-        <v>33.1075</v>
+        <v>33.40875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11125</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>30.47875</v>
+        <v>30.55</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.98875</v>
+        <v>0.99625</v>
       </c>
       <c r="N4" t="n">
-        <v>28.21125</v>
+        <v>27.8675</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0.86</v>
+        <v>0.965</v>
       </c>
       <c r="N5" t="n">
-        <v>25.51625</v>
+        <v>25.05375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>0.855</v>
+        <v>0.8025</v>
       </c>
       <c r="N6" t="n">
-        <v>22.99125</v>
+        <v>22.67625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.63125</v>
+        <v>0.61</v>
       </c>
       <c r="N7" t="n">
-        <v>20.58625</v>
+        <v>20.12875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.465</v>
+        <v>0.4575</v>
       </c>
       <c r="N8" t="n">
-        <v>17.73</v>
+        <v>17.25</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8261</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>877</v>
+      </c>
+      <c r="D75" t="n">
+        <v>577</v>
+      </c>
+      <c r="E75" t="n">
+        <v>300</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>196</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>223</v>
+      </c>
+      <c r="K75" t="n">
+        <v>179</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.91625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06000000000000005</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.03821656050955413</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.840000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1008668242710796</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.253731343283582</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.700000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09754811494858961</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
